--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U286"/>
+  <dimension ref="A1:U287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20186,6 +20186,75 @@
       <c r="U286" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="C287" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="D287" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="E287" t="n">
+        <v>374.48</v>
+      </c>
+      <c r="F287" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="G287" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="H287" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="I287" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="J287" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="K287" t="n">
+        <v>387.96</v>
+      </c>
+      <c r="L287" t="n">
+        <v>379.88</v>
+      </c>
+      <c r="M287" t="n">
+        <v>360.88</v>
+      </c>
+      <c r="N287" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="O287" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="P287" t="n">
+        <v>359.16</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>367</v>
+      </c>
+      <c r="R287" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="S287" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="T287" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20200,7 +20269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23143,6 +23212,16 @@
       </c>
       <c r="B294" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -23311,28 +23390,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02192510142733989</v>
+        <v>-0.02661085194008931</v>
       </c>
       <c r="J2" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K2" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005999931902018751</v>
+        <v>0.0008877347454294693</v>
       </c>
       <c r="M2" t="n">
-        <v>4.906996477867485</v>
+        <v>4.911829141933368</v>
       </c>
       <c r="N2" t="n">
-        <v>39.35903801274872</v>
+        <v>39.35517411080846</v>
       </c>
       <c r="O2" t="n">
-        <v>6.27367818849108</v>
+        <v>6.273370235432344</v>
       </c>
       <c r="P2" t="n">
-        <v>381.9646319947545</v>
+        <v>382.0188609054823</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23389,28 +23468,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02745127740181286</v>
+        <v>-0.03339073557843451</v>
       </c>
       <c r="J3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001155285690614072</v>
+        <v>0.00171066975782741</v>
       </c>
       <c r="M3" t="n">
-        <v>4.396873570041039</v>
+        <v>4.407061337920416</v>
       </c>
       <c r="N3" t="n">
-        <v>32.02594286924928</v>
+        <v>32.12886865415359</v>
       </c>
       <c r="O3" t="n">
-        <v>5.659146832275098</v>
+        <v>5.668233292142586</v>
       </c>
       <c r="P3" t="n">
-        <v>384.3174687777837</v>
+        <v>384.3862070399585</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23467,28 +23546,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008907692486513271</v>
+        <v>-0.01351069275226095</v>
       </c>
       <c r="J4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001534056771872461</v>
+        <v>0.0003538979775484785</v>
       </c>
       <c r="M4" t="n">
-        <v>3.738616743517631</v>
+        <v>3.748292229570407</v>
       </c>
       <c r="N4" t="n">
-        <v>25.42088097581166</v>
+        <v>25.46106937908641</v>
       </c>
       <c r="O4" t="n">
-        <v>5.041912432382346</v>
+        <v>5.045896290956287</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1539669766896</v>
+        <v>385.2072382060928</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23545,28 +23624,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04280243211382712</v>
+        <v>0.03695343914465366</v>
       </c>
       <c r="J5" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K5" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002938790360045296</v>
+        <v>0.0021948703080229</v>
       </c>
       <c r="M5" t="n">
-        <v>4.131211645209771</v>
+        <v>4.146921484393886</v>
       </c>
       <c r="N5" t="n">
-        <v>30.55331476662939</v>
+        <v>30.65489293696051</v>
       </c>
       <c r="O5" t="n">
-        <v>5.52750529322491</v>
+        <v>5.536686097022343</v>
       </c>
       <c r="P5" t="n">
-        <v>381.093353997908</v>
+        <v>381.1610452923356</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23623,28 +23702,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01497258538777293</v>
+        <v>-0.01822936966446289</v>
       </c>
       <c r="J6" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K6" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003365603238782988</v>
+        <v>0.0005018656180816317</v>
       </c>
       <c r="M6" t="n">
-        <v>4.356324483139518</v>
+        <v>4.359206076794987</v>
       </c>
       <c r="N6" t="n">
-        <v>32.73050569332918</v>
+        <v>32.68067787528123</v>
       </c>
       <c r="O6" t="n">
-        <v>5.721058092112785</v>
+        <v>5.716701660510301</v>
       </c>
       <c r="P6" t="n">
-        <v>377.8070677180625</v>
+        <v>377.8447589829559</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23701,28 +23780,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04957837438529531</v>
+        <v>0.04963328481007985</v>
       </c>
       <c r="J7" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K7" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002441034256017605</v>
+        <v>0.002466211836566923</v>
       </c>
       <c r="M7" t="n">
-        <v>4.961952065936245</v>
+        <v>4.944867017537255</v>
       </c>
       <c r="N7" t="n">
-        <v>49.37618068682448</v>
+        <v>49.20355506640067</v>
       </c>
       <c r="O7" t="n">
-        <v>7.026818674679494</v>
+        <v>7.014524578786553</v>
       </c>
       <c r="P7" t="n">
-        <v>373.0057798211444</v>
+        <v>373.0051443343605</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23779,28 +23858,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06263946026495774</v>
+        <v>-0.06119669026518965</v>
       </c>
       <c r="J8" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K8" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003225908624788443</v>
+        <v>0.003103691839080547</v>
       </c>
       <c r="M8" t="n">
-        <v>6.039520574001545</v>
+        <v>6.02385416611794</v>
       </c>
       <c r="N8" t="n">
-        <v>59.59487585647975</v>
+        <v>59.39918295359023</v>
       </c>
       <c r="O8" t="n">
-        <v>7.719771748988421</v>
+        <v>7.707086541202858</v>
       </c>
       <c r="P8" t="n">
-        <v>373.9191018569518</v>
+        <v>373.9024044580387</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23857,28 +23936,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.123857059969811</v>
+        <v>-0.1215426545927121</v>
       </c>
       <c r="J9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01655275121211597</v>
+        <v>0.01606534729812448</v>
       </c>
       <c r="M9" t="n">
-        <v>5.371818502854847</v>
+        <v>5.364115960658989</v>
       </c>
       <c r="N9" t="n">
-        <v>44.80130265138719</v>
+        <v>44.67728578081189</v>
       </c>
       <c r="O9" t="n">
-        <v>6.693377521953113</v>
+        <v>6.684106954620931</v>
       </c>
       <c r="P9" t="n">
-        <v>375.2182705951423</v>
+        <v>375.1914856260661</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23935,28 +24014,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09155997914874861</v>
+        <v>-0.08923094281735253</v>
       </c>
       <c r="J10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009918933532872765</v>
+        <v>0.009493520862128291</v>
       </c>
       <c r="M10" t="n">
-        <v>5.180597197802048</v>
+        <v>5.17219292181947</v>
       </c>
       <c r="N10" t="n">
-        <v>41.13252513195982</v>
+        <v>41.02175002554429</v>
       </c>
       <c r="O10" t="n">
-        <v>6.413464362726265</v>
+        <v>6.404822403903506</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7940779349813</v>
+        <v>381.7671236396228</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24013,28 +24092,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02413211447212983</v>
+        <v>-0.01920751060201703</v>
       </c>
       <c r="J11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003048522384411223</v>
+        <v>0.0001944059574252588</v>
       </c>
       <c r="M11" t="n">
-        <v>7.8723113493109</v>
+        <v>7.870189232433964</v>
       </c>
       <c r="N11" t="n">
-        <v>93.8722387642693</v>
+        <v>93.69175298852568</v>
       </c>
       <c r="O11" t="n">
-        <v>9.688768691854982</v>
+        <v>9.679450035437224</v>
       </c>
       <c r="P11" t="n">
-        <v>382.0671722240482</v>
+        <v>382.0101790267118</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24095,28 +24174,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08526620025736041</v>
+        <v>0.08941993415662636</v>
       </c>
       <c r="J12" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K12" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008959714936429553</v>
+        <v>0.009898309405865224</v>
       </c>
       <c r="M12" t="n">
-        <v>4.996834031362344</v>
+        <v>4.999342870229199</v>
       </c>
       <c r="N12" t="n">
-        <v>39.86121625267536</v>
+        <v>39.82551829152822</v>
       </c>
       <c r="O12" t="n">
-        <v>6.313573968258815</v>
+        <v>6.310746254725206</v>
       </c>
       <c r="P12" t="n">
-        <v>372.1043315034088</v>
+        <v>372.0563880269742</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24177,28 +24256,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1217388175206392</v>
+        <v>-0.1199956772230033</v>
       </c>
       <c r="J13" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K13" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02699302371114298</v>
+        <v>0.02643439058657571</v>
       </c>
       <c r="M13" t="n">
-        <v>3.924636394884895</v>
+        <v>3.918685985100633</v>
       </c>
       <c r="N13" t="n">
-        <v>26.23581749006183</v>
+        <v>26.16162172801458</v>
       </c>
       <c r="O13" t="n">
-        <v>5.122091124732343</v>
+        <v>5.114843275019733</v>
       </c>
       <c r="P13" t="n">
-        <v>361.8507046505519</v>
+        <v>361.8304585251425</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24255,28 +24334,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1903582993326532</v>
+        <v>-0.1921821740906427</v>
       </c>
       <c r="J14" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K14" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04336190442803889</v>
+        <v>0.04447997230096112</v>
       </c>
       <c r="M14" t="n">
-        <v>4.996694584446541</v>
+        <v>4.988560776413039</v>
       </c>
       <c r="N14" t="n">
-        <v>39.29625668746579</v>
+        <v>39.17912197785749</v>
       </c>
       <c r="O14" t="n">
-        <v>6.268672641593736</v>
+        <v>6.259322805053075</v>
       </c>
       <c r="P14" t="n">
-        <v>364.3843176838973</v>
+        <v>364.4054256667403</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24333,28 +24412,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1044189440908126</v>
+        <v>-0.1016764846983586</v>
       </c>
       <c r="J15" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K15" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01661212203598295</v>
+        <v>0.01586768029340935</v>
       </c>
       <c r="M15" t="n">
-        <v>4.351938089946104</v>
+        <v>4.346208456772554</v>
       </c>
       <c r="N15" t="n">
-        <v>31.72682098695214</v>
+        <v>31.66170566140803</v>
       </c>
       <c r="O15" t="n">
-        <v>5.632656654452865</v>
+        <v>5.626873524561222</v>
       </c>
       <c r="P15" t="n">
-        <v>361.9555103000963</v>
+        <v>361.9237713961228</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24411,28 +24490,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07732122402550624</v>
+        <v>-0.07674900264754413</v>
       </c>
       <c r="J16" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K16" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01103870683683728</v>
+        <v>0.01096407882347816</v>
       </c>
       <c r="M16" t="n">
-        <v>3.973928291894909</v>
+        <v>3.961937599297757</v>
       </c>
       <c r="N16" t="n">
-        <v>26.32853907593495</v>
+        <v>26.23847595910936</v>
       </c>
       <c r="O16" t="n">
-        <v>5.131134287458763</v>
+        <v>5.12235062828672</v>
       </c>
       <c r="P16" t="n">
-        <v>360.4808895409587</v>
+        <v>360.4742671350202</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24489,28 +24568,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05073039943495677</v>
+        <v>-0.04693581252370946</v>
       </c>
       <c r="J17" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K17" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00578000305843529</v>
+        <v>0.004971712403731621</v>
       </c>
       <c r="M17" t="n">
-        <v>3.369926822995938</v>
+        <v>3.37374227558719</v>
       </c>
       <c r="N17" t="n">
-        <v>21.76001625595321</v>
+        <v>21.77164873883028</v>
       </c>
       <c r="O17" t="n">
-        <v>4.664763258296525</v>
+        <v>4.666009937712337</v>
       </c>
       <c r="P17" t="n">
-        <v>363.3287839978037</v>
+        <v>363.2848686603782</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24567,28 +24646,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05086175352687594</v>
+        <v>0.05421903302270962</v>
       </c>
       <c r="J18" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K18" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003304663204321545</v>
+        <v>0.003777189040798157</v>
       </c>
       <c r="M18" t="n">
-        <v>4.350729128130989</v>
+        <v>4.348606773946666</v>
       </c>
       <c r="N18" t="n">
-        <v>38.35183123195914</v>
+        <v>38.28639759798106</v>
       </c>
       <c r="O18" t="n">
-        <v>6.192885533574728</v>
+        <v>6.187600310134864</v>
       </c>
       <c r="P18" t="n">
-        <v>366.0070370399318</v>
+        <v>365.9681827284245</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24645,28 +24724,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01118668472266759</v>
+        <v>0.01423970292117195</v>
       </c>
       <c r="J19" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K19" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0001572228933878206</v>
+        <v>0.0002564163847932344</v>
       </c>
       <c r="M19" t="n">
-        <v>4.624484641884106</v>
+        <v>4.621163043943128</v>
       </c>
       <c r="N19" t="n">
-        <v>39.11892864034789</v>
+        <v>39.03893119149574</v>
       </c>
       <c r="O19" t="n">
-        <v>6.254512662098294</v>
+        <v>6.248114210823594</v>
       </c>
       <c r="P19" t="n">
-        <v>370.3006534360838</v>
+        <v>370.2653203873253</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24723,28 +24802,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07293878462630674</v>
+        <v>-0.06936881353684447</v>
       </c>
       <c r="J20" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K20" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0106191733409341</v>
+        <v>0.009661443136251724</v>
       </c>
       <c r="M20" t="n">
-        <v>3.725951436707553</v>
+        <v>3.728030635917282</v>
       </c>
       <c r="N20" t="n">
-        <v>24.36453071076594</v>
+        <v>24.35697931783982</v>
       </c>
       <c r="O20" t="n">
-        <v>4.936044034524605</v>
+        <v>4.935279051668692</v>
       </c>
       <c r="P20" t="n">
-        <v>378.7319173734873</v>
+        <v>378.6906015494833</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24782,7 +24861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U286"/>
+  <dimension ref="A1:U287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55359,6 +55438,113 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-35.673508148612406,174.5082852402704</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>-35.67423492026127,174.5083657986253</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>-35.674954049474714,174.50847370538293</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-35.67567546157321,174.50856714375067</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-35.676397600179534,174.50869636055282</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-35.67711552914936,174.50885654911076</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-35.67783570631269,174.5089993807759</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-35.67855148922419,174.50915808468196</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-35.67921406580834,174.50940524706618</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-35.679758670281004,174.50996922275095</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-35.68047390493961,174.5102224127001</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-35.68123024463658,174.51000920945498</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-35.681960505280095,174.51008871867373</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-35.682668622391766,174.51031685621518</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-35.6833905810483,174.51045171867693</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-35.68409815955106,174.51068179758482</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-35.68480523052647,174.51087546407345</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>-35.68546550127454,174.51116446194283</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>-35.68605909573587,174.51166651528752</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U287"/>
+  <dimension ref="A1:U288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20253,6 +20253,75 @@
         <v>381.51</v>
       </c>
       <c r="U287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>376.51</v>
+      </c>
+      <c r="C288" t="n">
+        <v>377.14</v>
+      </c>
+      <c r="D288" t="n">
+        <v>379.2</v>
+      </c>
+      <c r="E288" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="F288" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="G288" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="H288" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="I288" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="J288" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="K288" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="L288" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="M288" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="N288" t="n">
+        <v>359.08</v>
+      </c>
+      <c r="O288" t="n">
+        <v>363.47</v>
+      </c>
+      <c r="P288" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="R288" t="n">
+        <v>370.47</v>
+      </c>
+      <c r="S288" t="n">
+        <v>372.46</v>
+      </c>
+      <c r="T288" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="U288" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20269,7 +20338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23222,6 +23291,16 @@
       </c>
       <c r="B295" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -23390,28 +23469,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02661085194008931</v>
+        <v>-0.03020532536575324</v>
       </c>
       <c r="J2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008877347454294693</v>
+        <v>0.001150418244079465</v>
       </c>
       <c r="M2" t="n">
-        <v>4.911829141933368</v>
+        <v>4.911386940180045</v>
       </c>
       <c r="N2" t="n">
-        <v>39.35517411080846</v>
+        <v>39.29701339450076</v>
       </c>
       <c r="O2" t="n">
-        <v>6.273370235432344</v>
+        <v>6.268732997544301</v>
       </c>
       <c r="P2" t="n">
-        <v>382.0188609054823</v>
+        <v>382.0605965978951</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23468,28 +23547,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03339073557843451</v>
+        <v>-0.03815606070167687</v>
       </c>
       <c r="J3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00171066975782741</v>
+        <v>0.002241004867934882</v>
       </c>
       <c r="M3" t="n">
-        <v>4.407061337920416</v>
+        <v>4.412724578354378</v>
       </c>
       <c r="N3" t="n">
-        <v>32.12886865415359</v>
+        <v>32.15570906770316</v>
       </c>
       <c r="O3" t="n">
-        <v>5.668233292142586</v>
+        <v>5.670600415097431</v>
       </c>
       <c r="P3" t="n">
-        <v>384.3862070399585</v>
+        <v>384.4415375766016</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23546,28 +23625,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01351069275226095</v>
+        <v>-0.01774892468273318</v>
       </c>
       <c r="J4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003538979775484785</v>
+        <v>0.0006129007417851051</v>
       </c>
       <c r="M4" t="n">
-        <v>3.748292229570407</v>
+        <v>3.756197334053744</v>
       </c>
       <c r="N4" t="n">
-        <v>25.46106937908641</v>
+        <v>25.48213790762004</v>
       </c>
       <c r="O4" t="n">
-        <v>5.045896290956287</v>
+        <v>5.047983548667728</v>
       </c>
       <c r="P4" t="n">
-        <v>385.2072382060928</v>
+        <v>385.256448625333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23624,28 +23703,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03695343914465366</v>
+        <v>0.03147969031927262</v>
       </c>
       <c r="J5" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K5" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0021948703080229</v>
+        <v>0.001597111987374777</v>
       </c>
       <c r="M5" t="n">
-        <v>4.146921484393886</v>
+        <v>4.160733267566187</v>
       </c>
       <c r="N5" t="n">
-        <v>30.65489293696051</v>
+        <v>30.73120139080729</v>
       </c>
       <c r="O5" t="n">
-        <v>5.536686097022343</v>
+        <v>5.543572980561119</v>
       </c>
       <c r="P5" t="n">
-        <v>381.1610452923356</v>
+        <v>381.2246013881159</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23702,28 +23781,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01822936966446289</v>
+        <v>-0.02176975485630557</v>
       </c>
       <c r="J6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005018656180816317</v>
+        <v>0.0007196925405389409</v>
       </c>
       <c r="M6" t="n">
-        <v>4.359206076794987</v>
+        <v>4.363486926984884</v>
       </c>
       <c r="N6" t="n">
-        <v>32.68067787528123</v>
+        <v>32.64341464474552</v>
       </c>
       <c r="O6" t="n">
-        <v>5.716701660510301</v>
+        <v>5.713441576208294</v>
       </c>
       <c r="P6" t="n">
-        <v>377.8447589829559</v>
+        <v>377.8858666529514</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23780,28 +23859,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04963328481007985</v>
+        <v>0.04949456603839665</v>
       </c>
       <c r="J7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002466211836566923</v>
+        <v>0.00247233039781658</v>
       </c>
       <c r="M7" t="n">
-        <v>4.944867017537255</v>
+        <v>4.928249473813478</v>
       </c>
       <c r="N7" t="n">
-        <v>49.20355506640067</v>
+        <v>49.03223171584096</v>
       </c>
       <c r="O7" t="n">
-        <v>7.014524578786553</v>
+        <v>7.002301886939819</v>
       </c>
       <c r="P7" t="n">
-        <v>373.0051443343605</v>
+        <v>373.0067550081092</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23858,28 +23937,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06119669026518965</v>
+        <v>-0.05971499956985477</v>
       </c>
       <c r="J8" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K8" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003103691839080547</v>
+        <v>0.002978902911196735</v>
       </c>
       <c r="M8" t="n">
-        <v>6.02385416611794</v>
+        <v>6.008394521109286</v>
       </c>
       <c r="N8" t="n">
-        <v>59.39918295359023</v>
+        <v>59.20563494915503</v>
       </c>
       <c r="O8" t="n">
-        <v>7.707086541202858</v>
+        <v>7.694519799776659</v>
       </c>
       <c r="P8" t="n">
-        <v>373.9024044580387</v>
+        <v>373.8852004395948</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23936,28 +24015,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1215426545927121</v>
+        <v>-0.1196224338883021</v>
       </c>
       <c r="J9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01606534729812448</v>
+        <v>0.01568614960533166</v>
       </c>
       <c r="M9" t="n">
-        <v>5.364115960658989</v>
+        <v>5.354509922343401</v>
       </c>
       <c r="N9" t="n">
-        <v>44.67728578081189</v>
+        <v>44.54415134613453</v>
       </c>
       <c r="O9" t="n">
-        <v>6.684106954620931</v>
+        <v>6.67414049493525</v>
       </c>
       <c r="P9" t="n">
-        <v>375.1914856260661</v>
+        <v>375.1691898037875</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24014,28 +24093,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08923094281735253</v>
+        <v>-0.08729843335142029</v>
       </c>
       <c r="J10" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K10" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009493520862128291</v>
+        <v>0.009158503589462685</v>
       </c>
       <c r="M10" t="n">
-        <v>5.17219292181947</v>
+        <v>5.162133986105663</v>
       </c>
       <c r="N10" t="n">
-        <v>41.02175002554429</v>
+        <v>40.90164201197419</v>
       </c>
       <c r="O10" t="n">
-        <v>6.404822403903506</v>
+        <v>6.395439157084851</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7671236396228</v>
+        <v>381.7446851316401</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24092,28 +24171,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01920751060201703</v>
+        <v>-0.01522551384717511</v>
       </c>
       <c r="J11" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K11" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001944059574252588</v>
+        <v>0.0001230276167746291</v>
       </c>
       <c r="M11" t="n">
-        <v>7.870189232433964</v>
+        <v>7.863207567139115</v>
       </c>
       <c r="N11" t="n">
-        <v>93.69175298852568</v>
+        <v>93.46221068393581</v>
       </c>
       <c r="O11" t="n">
-        <v>9.679450035437224</v>
+        <v>9.667585566413974</v>
       </c>
       <c r="P11" t="n">
-        <v>382.0101790267118</v>
+        <v>381.9639437727348</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24174,28 +24253,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08941993415662636</v>
+        <v>0.09375545267683048</v>
       </c>
       <c r="J12" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K12" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009898309405865224</v>
+        <v>0.01092681238650073</v>
       </c>
       <c r="M12" t="n">
-        <v>4.999342870229199</v>
+        <v>5.002593064761855</v>
       </c>
       <c r="N12" t="n">
-        <v>39.82551829152822</v>
+        <v>39.80028030309143</v>
       </c>
       <c r="O12" t="n">
-        <v>6.310746254725206</v>
+        <v>6.308746333709371</v>
       </c>
       <c r="P12" t="n">
-        <v>372.0563880269742</v>
+        <v>372.0061801269066</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24256,28 +24335,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1199956772230033</v>
+        <v>-0.1178025842040608</v>
       </c>
       <c r="J13" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K13" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02643439058657571</v>
+        <v>0.02567466354932246</v>
       </c>
       <c r="M13" t="n">
-        <v>3.918685985100633</v>
+        <v>3.91481375577289</v>
       </c>
       <c r="N13" t="n">
-        <v>26.16162172801458</v>
+        <v>26.09889621709189</v>
       </c>
       <c r="O13" t="n">
-        <v>5.114843275019733</v>
+        <v>5.108707881362164</v>
       </c>
       <c r="P13" t="n">
-        <v>361.8304585251425</v>
+        <v>361.8049021951449</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24334,28 +24413,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1921821740906427</v>
+        <v>-0.1922932400322552</v>
       </c>
       <c r="J14" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K14" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04447997230096112</v>
+        <v>0.04487423889943498</v>
       </c>
       <c r="M14" t="n">
-        <v>4.988560776413039</v>
+        <v>4.971748072207601</v>
       </c>
       <c r="N14" t="n">
-        <v>39.17912197785749</v>
+        <v>39.04268475014551</v>
       </c>
       <c r="O14" t="n">
-        <v>6.259322805053075</v>
+        <v>6.248414578926843</v>
       </c>
       <c r="P14" t="n">
-        <v>364.4054256667403</v>
+        <v>364.4067152614675</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24412,28 +24491,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1016764846983586</v>
+        <v>-0.09846318612743668</v>
       </c>
       <c r="J15" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K15" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01586768029340935</v>
+        <v>0.01498485857646059</v>
       </c>
       <c r="M15" t="n">
-        <v>4.346208456772554</v>
+        <v>4.34233943716828</v>
       </c>
       <c r="N15" t="n">
-        <v>31.66170566140803</v>
+        <v>31.61449174970726</v>
       </c>
       <c r="O15" t="n">
-        <v>5.626873524561222</v>
+        <v>5.622676564564893</v>
       </c>
       <c r="P15" t="n">
-        <v>361.9237713961228</v>
+        <v>361.8864615526756</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24490,28 +24569,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07674900264754413</v>
+        <v>-0.07663707425369698</v>
       </c>
       <c r="J16" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K16" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01096407882347816</v>
+        <v>0.0110201985088465</v>
       </c>
       <c r="M16" t="n">
-        <v>3.961937599297757</v>
+        <v>3.94850049287471</v>
       </c>
       <c r="N16" t="n">
-        <v>26.23847595910936</v>
+        <v>26.14712926577229</v>
       </c>
       <c r="O16" t="n">
-        <v>5.12235062828672</v>
+        <v>5.113426372382054</v>
       </c>
       <c r="P16" t="n">
-        <v>360.4742671350202</v>
+        <v>360.4729675262974</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24568,28 +24647,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04693581252370946</v>
+        <v>-0.04401162216931323</v>
       </c>
       <c r="J17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004971712403731621</v>
+        <v>0.004398939117420286</v>
       </c>
       <c r="M17" t="n">
-        <v>3.37374227558719</v>
+        <v>3.373867533028218</v>
       </c>
       <c r="N17" t="n">
-        <v>21.77164873883028</v>
+        <v>21.74805026848295</v>
       </c>
       <c r="O17" t="n">
-        <v>4.666009937712337</v>
+        <v>4.663480488699717</v>
       </c>
       <c r="P17" t="n">
-        <v>363.2848686603782</v>
+        <v>363.2509156734633</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24646,28 +24725,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05421903302270962</v>
+        <v>0.05650520890440798</v>
       </c>
       <c r="J18" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K18" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003777189040798157</v>
+        <v>0.00413081113410152</v>
       </c>
       <c r="M18" t="n">
-        <v>4.348606773946666</v>
+        <v>4.342266862297556</v>
       </c>
       <c r="N18" t="n">
-        <v>38.28639759798106</v>
+        <v>38.18493921110745</v>
       </c>
       <c r="O18" t="n">
-        <v>6.187600310134864</v>
+        <v>6.17939634682122</v>
       </c>
       <c r="P18" t="n">
-        <v>365.9681827284245</v>
+        <v>365.9416377739622</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24724,28 +24803,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01423970292117195</v>
+        <v>0.01559603366025546</v>
       </c>
       <c r="J19" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K19" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0002564163847932344</v>
+        <v>0.0003099804521374816</v>
       </c>
       <c r="M19" t="n">
-        <v>4.621163043943128</v>
+        <v>4.610700607617564</v>
       </c>
       <c r="N19" t="n">
-        <v>39.03893119149574</v>
+        <v>38.91415042611758</v>
       </c>
       <c r="O19" t="n">
-        <v>6.248114210823594</v>
+        <v>6.238120744752989</v>
       </c>
       <c r="P19" t="n">
-        <v>370.2653203873253</v>
+        <v>370.2495719324522</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24802,28 +24881,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06936881353684447</v>
+        <v>-0.0668188594246603</v>
       </c>
       <c r="J20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L20" t="n">
-        <v>0.009661443136251724</v>
+        <v>0.009027960491284848</v>
       </c>
       <c r="M20" t="n">
-        <v>3.728030635917282</v>
+        <v>3.725760452449918</v>
       </c>
       <c r="N20" t="n">
-        <v>24.35697931783982</v>
+        <v>24.31185204528419</v>
       </c>
       <c r="O20" t="n">
-        <v>4.935279051668692</v>
+        <v>4.930705025174817</v>
       </c>
       <c r="P20" t="n">
-        <v>378.6906015494833</v>
+        <v>378.6609938467992</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24861,7 +24940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U287"/>
+  <dimension ref="A1:U288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55545,6 +55624,113 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-35.67350701048841,174.50830019994874</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>-35.67423370681042,174.50838174842548</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>-35.67495358013872,174.5084780868566</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-35.675674867884894,174.50857139050026</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-35.676398278849,174.50869157117978</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-35.67711591627839,174.50885382817634</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-35.677835580565244,174.50900025108078</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-35.67855236603555,174.50915266613552</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-35.67921587975348,174.50940031099182</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-35.679763822094785,174.50995807010122</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-35.68047333143636,174.51022610281427</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-35.68122982574076,174.5100160402767</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-35.68195709846769,174.51011300070977</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-35.682667411575416,174.51032422131706</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-35.68339159297159,174.51044520644118</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-35.68409981118993,174.51067003772215</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-35.68480817013624,174.51086087578022</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>-35.68547357359316,174.51114237978808</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>-35.68606492276308,174.51165418048743</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0095/nzd0095.xlsx
+++ b/data/nzd0095/nzd0095.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U288"/>
+  <dimension ref="A1:U289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20322,6 +20322,75 @@
         <v>380.22</v>
       </c>
       <c r="U288" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="C289" t="n">
+        <v>378.45</v>
+      </c>
+      <c r="D289" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="E289" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="F289" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="G289" t="n">
+        <v>373.68</v>
+      </c>
+      <c r="H289" t="n">
+        <v>374.08</v>
+      </c>
+      <c r="I289" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="J289" t="n">
+        <v>382.22</v>
+      </c>
+      <c r="K289" t="n">
+        <v>386.74</v>
+      </c>
+      <c r="L289" t="n">
+        <v>380.42</v>
+      </c>
+      <c r="M289" t="n">
+        <v>361.63</v>
+      </c>
+      <c r="N289" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="O289" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="P289" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="R289" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="S289" t="n">
+        <v>371.73</v>
+      </c>
+      <c r="T289" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="U289" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20338,7 +20407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23301,6 +23370,16 @@
       </c>
       <c r="B296" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -23469,28 +23548,28 @@
         <v>0.0832</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03020532536575324</v>
+        <v>-0.03279422733575052</v>
       </c>
       <c r="J2" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K2" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001150418244079465</v>
+        <v>0.001365368197228989</v>
       </c>
       <c r="M2" t="n">
-        <v>4.911386940180045</v>
+        <v>4.906201501045288</v>
       </c>
       <c r="N2" t="n">
-        <v>39.29701339450076</v>
+        <v>39.20166602368946</v>
       </c>
       <c r="O2" t="n">
-        <v>6.268732997544301</v>
+        <v>6.261123383522277</v>
       </c>
       <c r="P2" t="n">
-        <v>382.0605965978951</v>
+        <v>382.0907542264939</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23547,28 +23626,28 @@
         <v>0.1134</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03815606070167687</v>
+        <v>-0.04186795544321782</v>
       </c>
       <c r="J3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002241004867934882</v>
+        <v>0.00271172721906654</v>
       </c>
       <c r="M3" t="n">
-        <v>4.412724578354378</v>
+        <v>4.413587811553604</v>
       </c>
       <c r="N3" t="n">
-        <v>32.15570906770316</v>
+        <v>32.12854785727591</v>
       </c>
       <c r="O3" t="n">
-        <v>5.670600415097431</v>
+        <v>5.668204994288396</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4415375766016</v>
+        <v>384.4847767352529</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23625,28 +23704,28 @@
         <v>0.1396</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01774892468273318</v>
+        <v>-0.02100181840660705</v>
       </c>
       <c r="J4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006129007417851051</v>
+        <v>0.0008626969628957593</v>
       </c>
       <c r="M4" t="n">
-        <v>3.756197334053744</v>
+        <v>3.759061547380737</v>
       </c>
       <c r="N4" t="n">
-        <v>25.48213790762004</v>
+        <v>25.45854510119984</v>
       </c>
       <c r="O4" t="n">
-        <v>5.047983548667728</v>
+        <v>5.04564615299169</v>
       </c>
       <c r="P4" t="n">
-        <v>385.256448625333</v>
+        <v>385.294340968084</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23703,28 +23782,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03147969031927262</v>
+        <v>0.02711771257925107</v>
       </c>
       <c r="J5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001597111987374777</v>
+        <v>0.001190751434131276</v>
       </c>
       <c r="M5" t="n">
-        <v>4.160733267566187</v>
+        <v>4.168617035812279</v>
       </c>
       <c r="N5" t="n">
-        <v>30.73120139080729</v>
+        <v>30.74117242882338</v>
       </c>
       <c r="O5" t="n">
-        <v>5.543572980561119</v>
+        <v>5.544472240783913</v>
       </c>
       <c r="P5" t="n">
-        <v>381.2246013881159</v>
+        <v>381.2754132404626</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23781,28 +23860,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02176975485630557</v>
+        <v>-0.0248847985383178</v>
       </c>
       <c r="J6" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K6" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0007196925405389409</v>
+        <v>0.0009460876799731732</v>
       </c>
       <c r="M6" t="n">
-        <v>4.363486926984884</v>
+        <v>4.365274014898347</v>
       </c>
       <c r="N6" t="n">
-        <v>32.64341464474552</v>
+        <v>32.58957331668769</v>
       </c>
       <c r="O6" t="n">
-        <v>5.713441576208294</v>
+        <v>5.708727819460978</v>
       </c>
       <c r="P6" t="n">
-        <v>377.8858666529514</v>
+        <v>377.9221532066795</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23859,28 +23938,28 @@
         <v>0.0907</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04949456603839665</v>
+        <v>0.04899742962891847</v>
       </c>
       <c r="J7" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K7" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00247233039781658</v>
+        <v>0.002442602670740146</v>
       </c>
       <c r="M7" t="n">
-        <v>4.928249473813478</v>
+        <v>4.913302675287525</v>
       </c>
       <c r="N7" t="n">
-        <v>49.03223171584096</v>
+        <v>48.86349645339605</v>
       </c>
       <c r="O7" t="n">
-        <v>7.002301886939819</v>
+        <v>6.990242946664733</v>
       </c>
       <c r="P7" t="n">
-        <v>373.0067550081092</v>
+        <v>373.012546055964</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23937,28 +24016,28 @@
         <v>0.0772</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05971499956985477</v>
+        <v>-0.05836178019894057</v>
       </c>
       <c r="J8" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K8" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002978902911196735</v>
+        <v>0.002868318358976052</v>
       </c>
       <c r="M8" t="n">
-        <v>6.008394521109286</v>
+        <v>5.992520138902355</v>
       </c>
       <c r="N8" t="n">
-        <v>59.20563494915503</v>
+        <v>59.01128914323047</v>
       </c>
       <c r="O8" t="n">
-        <v>7.694519799776659</v>
+        <v>7.681880573351194</v>
       </c>
       <c r="P8" t="n">
-        <v>373.8852004395948</v>
+        <v>373.8694370435012</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24015,28 +24094,28 @@
         <v>0.1236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1196224338883021</v>
+        <v>-0.11735914623198</v>
       </c>
       <c r="J9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01568614960533166</v>
+        <v>0.0152173777391521</v>
       </c>
       <c r="M9" t="n">
-        <v>5.354509922343401</v>
+        <v>5.346498389368413</v>
       </c>
       <c r="N9" t="n">
-        <v>44.54415134613453</v>
+        <v>44.42089621111182</v>
       </c>
       <c r="O9" t="n">
-        <v>6.67414049493525</v>
+        <v>6.664900315166898</v>
       </c>
       <c r="P9" t="n">
-        <v>375.1691898037875</v>
+        <v>375.1428251946433</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24093,28 +24172,28 @@
         <v>0.1802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08729843335142029</v>
+        <v>-0.08517946207291664</v>
       </c>
       <c r="J10" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K10" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009158503589462685</v>
+        <v>0.008787513434675653</v>
       </c>
       <c r="M10" t="n">
-        <v>5.162133986105663</v>
+        <v>5.152838891351184</v>
       </c>
       <c r="N10" t="n">
-        <v>40.90164201197419</v>
+        <v>40.78715627592702</v>
       </c>
       <c r="O10" t="n">
-        <v>6.395439157084851</v>
+        <v>6.386482308432947</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7446851316401</v>
+        <v>381.7200016366414</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24171,28 +24250,28 @@
         <v>0.0559</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01522551384717511</v>
+        <v>-0.01134074718488889</v>
       </c>
       <c r="J11" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K11" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001230276167746291</v>
+        <v>6.874634141051938e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>7.863207567139115</v>
+        <v>7.856223699657473</v>
       </c>
       <c r="N11" t="n">
-        <v>93.46221068393581</v>
+        <v>93.23023279485099</v>
       </c>
       <c r="O11" t="n">
-        <v>9.667585566413974</v>
+        <v>9.655580396581605</v>
       </c>
       <c r="P11" t="n">
-        <v>381.9639437727348</v>
+        <v>381.9186908618282</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24253,28 +24332,28 @@
         <v>0.0639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09375545267683048</v>
+        <v>0.09817198335542343</v>
       </c>
       <c r="J12" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K12" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01092681238650073</v>
+        <v>0.01202824869492336</v>
       </c>
       <c r="M12" t="n">
-        <v>5.002593064761855</v>
+        <v>5.006036548425613</v>
       </c>
       <c r="N12" t="n">
-        <v>39.80028030309143</v>
+        <v>39.78039309391487</v>
       </c>
       <c r="O12" t="n">
-        <v>6.308746333709371</v>
+        <v>6.307169975029599</v>
       </c>
       <c r="P12" t="n">
-        <v>372.0061801269066</v>
+        <v>371.9548655340326</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24335,28 +24414,28 @@
         <v>0.1547</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1178025842040608</v>
+        <v>-0.1155365859246643</v>
       </c>
       <c r="J13" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K13" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02567466354932246</v>
+        <v>0.02488696682531555</v>
       </c>
       <c r="M13" t="n">
-        <v>3.91481375577289</v>
+        <v>3.911330998292105</v>
       </c>
       <c r="N13" t="n">
-        <v>26.09889621709189</v>
+        <v>26.03880324845455</v>
       </c>
       <c r="O13" t="n">
-        <v>5.108707881362164</v>
+        <v>5.102823066544102</v>
       </c>
       <c r="P13" t="n">
-        <v>361.8049021951449</v>
+        <v>361.7784097985943</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24413,28 +24492,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1922932400322552</v>
+        <v>-0.1908722630381413</v>
       </c>
       <c r="J14" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K14" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04487423889943498</v>
+        <v>0.04457269555458732</v>
       </c>
       <c r="M14" t="n">
-        <v>4.971748072207601</v>
+        <v>4.960402124979873</v>
       </c>
       <c r="N14" t="n">
-        <v>39.04268475014551</v>
+        <v>38.91950187718587</v>
       </c>
       <c r="O14" t="n">
-        <v>6.248414578926843</v>
+        <v>6.238549661354462</v>
       </c>
       <c r="P14" t="n">
-        <v>364.4067152614675</v>
+        <v>364.3901625696574</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24491,28 +24570,28 @@
         <v>0.0871</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.09846318612743668</v>
+        <v>-0.09627502303537917</v>
       </c>
       <c r="J15" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K15" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01498485857646059</v>
+        <v>0.01443724251710998</v>
       </c>
       <c r="M15" t="n">
-        <v>4.34233943716828</v>
+        <v>4.335156748441674</v>
       </c>
       <c r="N15" t="n">
-        <v>31.61449174970726</v>
+        <v>31.53408057419927</v>
       </c>
       <c r="O15" t="n">
-        <v>5.622676564564893</v>
+        <v>5.615521398249611</v>
       </c>
       <c r="P15" t="n">
-        <v>361.8864615526756</v>
+        <v>361.8609720553487</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24569,28 +24648,28 @@
         <v>0.1227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07663707425369698</v>
+        <v>-0.07566890856060345</v>
       </c>
       <c r="J16" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K16" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0110201985088465</v>
+        <v>0.01083052000743789</v>
       </c>
       <c r="M16" t="n">
-        <v>3.94850049287471</v>
+        <v>3.937927722871885</v>
       </c>
       <c r="N16" t="n">
-        <v>26.14712926577229</v>
+        <v>26.06208861571896</v>
       </c>
       <c r="O16" t="n">
-        <v>5.113426372382054</v>
+        <v>5.105104172856707</v>
       </c>
       <c r="P16" t="n">
-        <v>360.4729675262974</v>
+        <v>360.4616895475509</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24647,28 +24726,28 @@
         <v>0.1412</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04401162216931323</v>
+        <v>-0.04115582194147906</v>
       </c>
       <c r="J17" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K17" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004398939117420286</v>
+        <v>0.003870974112445302</v>
       </c>
       <c r="M17" t="n">
-        <v>3.373867533028218</v>
+        <v>3.373619980061869</v>
       </c>
       <c r="N17" t="n">
-        <v>21.74805026848295</v>
+        <v>21.72254800865803</v>
       </c>
       <c r="O17" t="n">
-        <v>4.663480488699717</v>
+        <v>4.660745434869623</v>
       </c>
       <c r="P17" t="n">
-        <v>363.2509156734633</v>
+        <v>363.2176489976209</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24725,28 +24804,28 @@
         <v>0.1102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05650520890440798</v>
+        <v>0.05908179490498636</v>
       </c>
       <c r="J18" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K18" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00413081113410152</v>
+        <v>0.004546063650661236</v>
       </c>
       <c r="M18" t="n">
-        <v>4.342266862297556</v>
+        <v>4.337007469010312</v>
       </c>
       <c r="N18" t="n">
-        <v>38.18493921110745</v>
+        <v>38.0930630902371</v>
       </c>
       <c r="O18" t="n">
-        <v>6.17939634682122</v>
+        <v>6.171957800425818</v>
       </c>
       <c r="P18" t="n">
-        <v>365.9416377739622</v>
+        <v>365.9116236117579</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24803,28 +24882,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01559603366025546</v>
+        <v>0.01638716755231805</v>
       </c>
       <c r="J19" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K19" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0003099804521374816</v>
+        <v>0.0003449617021198392</v>
       </c>
       <c r="M19" t="n">
-        <v>4.610700607617564</v>
+        <v>4.597940886890391</v>
       </c>
       <c r="N19" t="n">
-        <v>38.91415042611758</v>
+        <v>38.78286995322823</v>
       </c>
       <c r="O19" t="n">
-        <v>6.238120744752989</v>
+        <v>6.227589417521697</v>
       </c>
       <c r="P19" t="n">
-        <v>370.2495719324522</v>
+        <v>370.2403561636185</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24881,28 +24960,28 @@
         <v>0.1144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0668188594246603</v>
+        <v>-0.06515639447724697</v>
       </c>
       <c r="J20" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K20" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L20" t="n">
-        <v>0.009027960491284848</v>
+        <v>0.008651317398786773</v>
       </c>
       <c r="M20" t="n">
-        <v>3.725760452449918</v>
+        <v>3.719826496034567</v>
       </c>
       <c r="N20" t="n">
-        <v>24.31185204528419</v>
+        <v>24.24438402534895</v>
       </c>
       <c r="O20" t="n">
-        <v>4.930705025174817</v>
+        <v>4.923858652048102</v>
       </c>
       <c r="P20" t="n">
-        <v>378.6609938467992</v>
+        <v>378.6416281075693</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24940,7 +25019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U288"/>
+  <dimension ref="A1:U289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55731,6 +55810,113 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-35.673505947679764,174.5083141696479</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>-35.674232610518516,174.50839615824447</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>-35.67495213692951,174.50849155988766</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-35.6756727671404,174.5085864174598</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-35.67639752305799,174.50869690479973</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-35.67711665956597,174.5088486039822</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-35.67783581634169,174.50899861925913</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-35.67855150676042,174.509157976311</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-35.679214843213416,174.50940313160578</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-35.67976408856789,174.50995749324</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-35.68047299408146,174.51022827346964</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-35.6812297379077,174.51001747254574</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-35.6819539971948,174.51013510498274</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-35.68266976198322,174.51030992435437</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-35.68338967031704,174.510457579689</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-35.68409987236173,174.51066960217167</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-35.68480721908622,174.5108655955223</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>-35.685476264365164,174.51113501906883</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>-35.68607007222795,174.51164327996491</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
